--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484090_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484090_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2222</v>
+        <v>7.717</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0547</v>
+        <v>4.3811</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1675</v>
+        <v>3.3358</v>
       </c>
       <c r="G2" t="n">
         <v>3.4347</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7356</v>
+        <v>-0.2409</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2639</v>
+        <v>0.0625</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4717</v>
+        <v>-0.3034</v>
       </c>
       <c r="V2" t="n">
         <v>1.349</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3041</v>
+        <v>3.3423</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3068</v>
+        <v>1.2048</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9973</v>
+        <v>2.1376</v>
       </c>
       <c r="G3" t="n">
         <v>1.5445</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2919</v>
+        <v>-0.2537</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4025</v>
+        <v>0.3005</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6944</v>
+        <v>-0.5541</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3254</v>
+        <v>2.6923</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3114</v>
+        <v>1.5203</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6368</v>
+        <v>1.172</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4102</v>
+        <v>1.5788</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2872</v>
+        <v>0.0501</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.123</v>
+        <v>1.5287</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3117</v>
+        <v>1.6183</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7544999999999999</v>
+        <v>1.0484</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5572</v>
+        <v>0.5699</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0986</v>
+        <v>-0.0395</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5327</v>
+        <v>-0.9983</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4341</v>
+        <v>0.9588</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6842</v>
+        <v>-0.9026</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6586</v>
+        <v>-0.5271</v>
       </c>
       <c r="U4" t="n">
-        <v>2.0256</v>
+        <v>-0.3756</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9405</v>
+        <v>2.4129</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6745</v>
+        <v>2.4129</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9756</v>
+        <v>1.4152</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1122</v>
+        <v>-0.4447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8633</v>
+        <v>1.8599</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5788</v>
+        <v>-1.1559</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0501</v>
+        <v>-2.6096</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5287</v>
+        <v>1.4537</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6183</v>
+        <v>-0.6817</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0484</v>
+        <v>-0.885</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5699</v>
+        <v>0.2034</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0395</v>
+        <v>-0.4742</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9983</v>
+        <v>-1.7245</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9588</v>
+        <v>1.2504</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>3.1741</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6194</v>
+        <v>0.1941</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9352</v>
+        <v>0.431</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6842</v>
+        <v>-0.2368</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4129</v>
+        <v>0.1947</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4129</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. MESA RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9075</v>
+        <v>0.9865</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0366</v>
+        <v>0.7946</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9441</v>
+        <v>0.1919</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1559</v>
+        <v>0.5444</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6096</v>
+        <v>0.5444</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4537</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6817</v>
+        <v>0.9476</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.885</v>
+        <v>0.9476</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2034</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4742</v>
+        <v>-0.4032</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7245</v>
+        <v>-0.4032</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2504</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1741</v>
+        <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6864</v>
+        <v>0.5215</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8391</v>
+        <v>0.5215</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1526</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1947</v>
+        <v>-0.6745</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.6745</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MESA RUIZ</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7007</v>
+        <v>0.9009</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5088</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1919</v>
+        <v>1.6102</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5444</v>
+        <v>-0.1902</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5444</v>
+        <v>0.0352</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.2254</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9476</v>
+        <v>-0.5392</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9476</v>
+        <v>0.1008</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4032</v>
+        <v>0.349</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4032</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4146</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2357</v>
+        <v>0.0992</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2357</v>
+        <v>-0.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2692</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6408</v>
+        <v>0.8752</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9133</v>
+        <v>0.87</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5541</v>
+        <v>0.0052</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1902</v>
+        <v>-2.8688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0352</v>
+        <v>-3.4065</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2254</v>
+        <v>0.5377</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5392</v>
+        <v>-0.6819</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1008</v>
+        <v>-1.3296</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.64</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.349</v>
+        <v>-2.1869</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-2.0769</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>-0.11</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.161</v>
+        <v>0.2877</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3741</v>
+        <v>0.0795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2131</v>
+        <v>0.2082</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2808</v>
+        <v>-0.1443</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3598</v>
+        <v>-0.5185</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.079</v>
+        <v>0.3742</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8688</v>
+        <v>-0.5524</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4065</v>
+        <v>0.7859</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5377</v>
+        <v>-1.3383</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6819</v>
+        <v>0.9607</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3296</v>
+        <v>2.3186</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6477000000000001</v>
+        <v>-1.3578</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1869</v>
+        <v>-1.5132</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0769</v>
+        <v>-1.5327</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.11</v>
+        <v>0.0195</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3066</v>
+        <v>0.2693</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4307</v>
+        <v>0.5046</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1241</v>
+        <v>-0.2353</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4724</v>
+        <v>0.3373</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9113</v>
+        <v>-0.511</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7968</v>
+        <v>-3.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8855</v>
+        <v>2.739</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6097</v>
+        <v>-2.4102</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-2.2872</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5442</v>
+        <v>-0.123</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6802</v>
+        <v>-1.3117</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6802</v>
+        <v>-0.5572</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.0986</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-1.5327</v>
       </c>
       <c r="O11" t="n">
-        <v>0.136</v>
+        <v>0.4341</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>2.9758</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0436</v>
+        <v>1.8478</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1247</v>
+        <v>0.72</v>
       </c>
       <c r="U11" t="n">
-        <v>0.081</v>
+        <v>1.1278</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3373</v>
+        <v>-0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3329</v>
+        <v>-0.6792</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5388</v>
+        <v>-1.5927</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2059</v>
+        <v>0.9136</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5524</v>
+        <v>-0.6097</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7859</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3383</v>
+        <v>-0.5442</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9607</v>
+        <v>-0.6802</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3186</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3578</v>
+        <v>-0.6802</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5132</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5327</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0195</v>
+        <v>0.136</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9193</v>
+        <v>0.1885</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5157</v>
+        <v>0.0794</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4036</v>
+        <v>0.1091</v>
       </c>
       <c r="V12" t="n">
         <v>0.3373</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8638</v>
+        <v>-2.3459</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3089</v>
+        <v>-1.8191</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.5268</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1773</v>
@@ -1468,13 +1468,13 @@
         <v>0.9919</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3135</v>
+        <v>-0.1686</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1451</v>
+        <v>0.6349</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8316</v>
+        <v>-0.8035</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7062</v>
+        <v>14.7061</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4968000000000001</v>
+        <v>0.4968999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2093</v>
+        <v>14.2094</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.801800000000001</v>
+        <v>-2.8018</v>
       </c>
       <c r="H14" t="n">
         <v>-13.555</v>
@@ -1522,7 +1522,7 @@
         <v>2.921100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8997999999999999</v>
+        <v>-0.8997999999999997</v>
       </c>
       <c r="L14" t="n">
         <v>3.8212</v>
@@ -1540,19 +1540,19 @@
         <v>10.911</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.927099999999999</v>
+        <v>-8.927100000000001</v>
       </c>
       <c r="R14" t="n">
         <v>19.8385</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8424</v>
+        <v>1.8423</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6367</v>
+        <v>2.6368</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7943000000000005</v>
+        <v>-0.7944000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>4.7546</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9224</v>
+        <v>4.0349</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2863</v>
+        <v>3.5518</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6361</v>
+        <v>0.4831</v>
       </c>
       <c r="G15" t="n">
         <v>3.9179</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7037</v>
+        <v>0.8162</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4885</v>
+        <v>0.754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2152</v>
+        <v>0.0622</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6992</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.776</v>
+        <v>0.7427</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1903</v>
+        <v>-2.1447</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5857</v>
+        <v>2.8874</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2797</v>
+        <v>3.7867</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2927</v>
+        <v>3.2957</v>
       </c>
       <c r="I16" t="n">
-        <v>0.013</v>
+        <v>0.491</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4287</v>
+        <v>2.2512</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4287</v>
+        <v>2.3239</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.0727</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7083</v>
+        <v>1.5355</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7213000000000001</v>
+        <v>0.9718</v>
       </c>
       <c r="O16" t="n">
-        <v>0.013</v>
+        <v>0.5637</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3887</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-4.9596</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6245</v>
+        <v>-0.2537</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4795</v>
+        <v>-0.0396</v>
       </c>
       <c r="U16" t="n">
-        <v>0.145</v>
+        <v>-0.2141</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8198</v>
+        <v>0.3838</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.2194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3507</v>
+        <v>-0.1967</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3488</v>
+        <v>-0.83</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6995</v>
+        <v>0.6333</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7867</v>
+        <v>-0.2797</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2957</v>
+        <v>-0.2927</v>
       </c>
       <c r="I17" t="n">
-        <v>0.491</v>
+        <v>0.013</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2512</v>
+        <v>0.4287</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3239</v>
+        <v>0.4287</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0727</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5355</v>
+        <v>-0.7083</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9718</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5637</v>
+        <v>0.013</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.1741</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.9596</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.6518</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2436</v>
+        <v>0.4592</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.402</v>
+        <v>0.1926</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3838</v>
+        <v>0.8198</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2194</v>
+        <v>0.5538999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0042</v>
+        <v>-1.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.357</v>
+        <v>-1.501</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3528</v>
+        <v>0.3821</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8761</v>
+        <v>-0.6539</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0352</v>
+        <v>0.5535</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8408</v>
+        <v>-1.2074</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0013</v>
+        <v>-0.2371</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2087</v>
+        <v>0.3226</v>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>-0.5597</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8748</v>
+        <v>-0.4168</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2439</v>
+        <v>0.2309</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3691</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4653</v>
+        <v>0.8375</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0372</v>
+        <v>0.4026</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4281</v>
+        <v>0.4349</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8198</v>
+        <v>-1.3024</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3373</v>
+        <v>-0.6745</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4826</v>
+        <v>-0.6279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1213</v>
+        <v>-1.3197</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0111</v>
+        <v>-2.9489</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1101</v>
+        <v>1.6291</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6539</v>
+        <v>0.8761</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5535</v>
+        <v>0.0352</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2074</v>
+        <v>0.8408</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2371</v>
+        <v>0.0013</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3226</v>
+        <v>-1.2087</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5597</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4168</v>
+        <v>0.8748</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2309</v>
+        <v>1.2439</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.3691</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.165</v>
+        <v>-0.7808</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1076</v>
+        <v>-0.6291</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0574</v>
+        <v>-0.1518</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3024</v>
+        <v>-0.8198</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6745</v>
+        <v>-0.3373</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6279</v>
+        <v>-0.4826</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1617</v>
+        <v>-1.3685</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8813</v>
+        <v>-0.8933</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2804</v>
+        <v>-0.4752</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1023</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4688</v>
+        <v>3.0739</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6335</v>
+        <v>-2.1339</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.64</v>
+        <v>0.4273</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.5807</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>-2.1534</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4623</v>
+        <v>0.5127</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4688</v>
+        <v>0.4932</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0065</v>
+        <v>0.0195</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2658</v>
+        <v>-0.6377</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2494</v>
+        <v>-0.3287</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0165</v>
+        <v>-0.309</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3292</v>
+        <v>-1.8944</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3014</v>
+        <v>-0.2678</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0278</v>
+        <v>-1.6266</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.3057</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0739</v>
+        <v>1.1893</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1339</v>
+        <v>-1.495</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4273</v>
+        <v>1.5403</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5807</v>
+        <v>1.5779</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1534</v>
+        <v>-0.0376</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5127</v>
+        <v>-1.846</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4932</v>
+        <v>-0.3886</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0195</v>
+        <v>-1.4574</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5984</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7368</v>
+        <v>-0.1416</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8616</v>
+        <v>0.1416</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4724</v>
+        <v>-0.7952</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4724</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.663</v>
+        <v>-2.2459</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.8813</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9871</v>
+        <v>-0.3646</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3057</v>
+        <v>-1.1023</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1893</v>
+        <v>-0.4688</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.495</v>
+        <v>-0.6335</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5403</v>
+        <v>-0.64</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5779</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0376</v>
+        <v>-0.64</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.846</v>
+        <v>-0.4623</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3886</v>
+        <v>-0.4688</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4574</v>
+        <v>0.0065</v>
       </c>
       <c r="P22" t="n">
         <v>-0.7935</v>
@@ -2170,22 +2170,22 @@
         <v>0.1984</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5498</v>
+        <v>-0.2494</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2188</v>
+        <v>-0.1006</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7952</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0458</v>
+        <v>-3.9915</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6949</v>
+        <v>-2.1847</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3509</v>
+        <v>-1.8067</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5514</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3571</v>
+        <v>0.6972</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0679</v>
+        <v>0.4422</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2892</v>
+        <v>0.255</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7486</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.43</v>
+        <v>-4.6274</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4154</v>
+        <v>-5.1093</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0146</v>
+        <v>0.4819</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8257</v>
@@ -2326,13 +2326,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9046</v>
+        <v>-0.102</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1813</v>
+        <v>0.1248</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.2268</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1206</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.7061</v>
+        <v>-11.9854</v>
       </c>
       <c r="E25" t="n">
         <v>-14.2092</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4968000000000002</v>
+        <v>2.2238</v>
       </c>
       <c r="G25" t="n">
         <v>2.802</v>
@@ -2383,13 +2383,13 @@
         <v>12.6551</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.931899999999999</v>
+        <v>-6.9319</v>
       </c>
       <c r="M25" t="n">
         <v>-2.9211</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8999999999999997</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-3.8212</v>
@@ -2401,22 +2401,22 @@
         <v>-19.8382</v>
       </c>
       <c r="R25" t="n">
-        <v>8.9274</v>
+        <v>8.927399999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8423</v>
+        <v>0.8785000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7943999999999999</v>
+        <v>0.7944</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6367</v>
+        <v>0.08399999999999996</v>
       </c>
       <c r="V25" t="n">
         <v>-4.754599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.8884</v>
+        <v>-0.8884000000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-3.8661</v>
